--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_unityProjects\ComputerBasics_DaniTech_Work\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7A7E03-C813-4D09-9761-6C15C6D4D315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AA29C2-62F4-4F55-9EB3-FCECC3E85D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10425" yWindow="1260" windowWidth="19815" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="108" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
   <si>
     <t>(name)</t>
   </si>
@@ -42,51 +42,193 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Weapon_Sword_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>검</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>고유 ID</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>석기시대의 검이다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_Braclet_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법팔찌</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법을 사용할 수 있는 팔찌</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_CoffeeCup_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>커피</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>일순간 잉여가 될 수 있는 마법의 커피. 시공간을 분리시킨다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>Weapon_PT_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본적인 한손 권총으로 가볍고, 반동이 적어 사용감이 좋다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PT2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PT 권총에서 강한 화력을 보강해, 일반 좀비는 한방에 보내버린다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_PT2_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_R0_3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>R0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사격 속도, 데미지, 탄창량 무엇하나 뛰어나지는 않지만, 꿇리지도 않는다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SG</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적이 멀리 있을 수록 데미지는 떨어지지만, 가까이 있다면 한번에 죽이기도 쉽다. </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_SG_4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_MG_5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MG</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠른 사격 속도에 중점을 둔 화기로 총알이 금세 동나고 한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_SR_6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SR</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>느리지만 확실하게 한발에 여러마리의 적을 한방에 죽인다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_GN_7</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GN</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭉쳐있는 적에 효과적인 투척무기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_HK_8</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HK</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 회복할 수 있는 키트. 사용하는 동안 무방비에 조심하자.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MD</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 빠르게 회복할 수 있지만 효과는 일시적이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 일시적으로 빠르게 회복하며, 지치지 않게 해준다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectiveRange</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RPM</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capacity</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capacity2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconPath</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_AD</t>
+  </si>
+  <si>
+    <t>Icon/Icon_GN</t>
+  </si>
+  <si>
+    <t>Icon/Icon_HK</t>
+  </si>
+  <si>
+    <t>Weapon_MK_9</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_AD_10</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_MD</t>
+  </si>
+  <si>
+    <t>Icon/Icon_MG</t>
+  </si>
+  <si>
+    <t>Icon/Icon_PT</t>
+  </si>
+  <si>
+    <t>Icon/Icon_R0</t>
+  </si>
+  <si>
+    <t>Icon/Icon_RT2</t>
+  </si>
+  <si>
+    <t>Icon/Icon_SG</t>
+  </si>
+  <si>
+    <t>Icon/Icon_SR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -126,8 +268,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,8 +312,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2F2DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -188,11 +348,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -217,6 +403,28 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -436,17 +644,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -461,6 +669,24 @@
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -472,23 +698,51 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="D3" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="D4" s="16">
+        <v>20</v>
+      </c>
+      <c r="E4" s="16">
+        <v>50</v>
+      </c>
+      <c r="F4" s="16">
+        <v>40</v>
+      </c>
+      <c r="G4" s="16">
+        <v>8</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -498,20 +752,30 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="D5" s="16">
+        <v>50</v>
+      </c>
+      <c r="E5" s="16">
+        <v>50</v>
+      </c>
+      <c r="F5" s="16">
+        <v>50</v>
+      </c>
+      <c r="G5" s="16">
+        <v>8</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -529,12 +793,24 @@
       <c r="C6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="D6" s="16">
+        <v>35</v>
+      </c>
+      <c r="E6" s="16">
+        <v>60</v>
+      </c>
+      <c r="F6" s="16">
+        <v>65</v>
+      </c>
+      <c r="G6" s="16">
+        <v>30</v>
+      </c>
+      <c r="H6" s="18">
+        <v>150</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -543,15 +819,33 @@
       <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="A7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="16">
+        <v>100</v>
+      </c>
+      <c r="E7" s="16">
+        <v>50</v>
+      </c>
+      <c r="F7" s="16">
+        <v>30</v>
+      </c>
+      <c r="G7" s="16">
+        <v>12</v>
+      </c>
+      <c r="H7" s="18">
+        <v>72</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -560,15 +854,33 @@
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="16">
+        <v>25</v>
+      </c>
+      <c r="E8" s="16">
+        <v>100</v>
+      </c>
+      <c r="F8" s="16">
+        <v>50</v>
+      </c>
+      <c r="G8" s="16">
+        <v>50</v>
+      </c>
+      <c r="H8" s="18">
+        <v>200</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>47</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -577,15 +889,33 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="16">
+        <v>100</v>
+      </c>
+      <c r="E9" s="16">
+        <v>20</v>
+      </c>
+      <c r="F9" s="16">
+        <v>80</v>
+      </c>
+      <c r="G9" s="16">
+        <v>10</v>
+      </c>
+      <c r="H9" s="18">
+        <v>50</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -594,15 +924,33 @@
       <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="16">
+        <v>100</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>42</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -611,15 +959,33 @@
       <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="A11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>43</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -628,15 +994,33 @@
       <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>46</v>
+      </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -645,15 +1029,33 @@
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="A13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="16">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="18">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>41</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1769,5 +2171,6 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AA29C2-62F4-4F55-9EB3-FCECC3E85D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961F90AC-D9CC-46B4-A82C-FB6A8A2BEC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="108" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2856" yWindow="780" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -378,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -418,7 +418,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -713,7 +712,7 @@
       <c r="H3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="18" t="s">
         <v>40</v>
       </c>
     </row>
@@ -739,7 +738,9 @@
       <c r="G4" s="16">
         <v>8</v>
       </c>
-      <c r="H4" s="17"/>
+      <c r="H4" s="16">
+        <v>-1</v>
+      </c>
       <c r="I4" s="16" t="s">
         <v>48</v>
       </c>
@@ -772,7 +773,9 @@
       <c r="G5" s="16">
         <v>8</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="16">
+        <v>-1</v>
+      </c>
       <c r="I5" s="16" t="s">
         <v>50</v>
       </c>
@@ -805,7 +808,7 @@
       <c r="G6" s="16">
         <v>30</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <v>150</v>
       </c>
       <c r="I6" s="16" t="s">
@@ -840,7 +843,7 @@
       <c r="G7" s="16">
         <v>12</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="17">
         <v>72</v>
       </c>
       <c r="I7" s="16" t="s">
@@ -875,7 +878,7 @@
       <c r="G8" s="16">
         <v>50</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <v>200</v>
       </c>
       <c r="I8" s="16" t="s">
@@ -910,7 +913,7 @@
       <c r="G9" s="16">
         <v>10</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="17">
         <v>50</v>
       </c>
       <c r="I9" s="16" t="s">
@@ -945,7 +948,7 @@
       <c r="G10" s="16">
         <v>0</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="17">
         <v>0</v>
       </c>
       <c r="I10" s="16" t="s">
@@ -980,7 +983,7 @@
       <c r="G11" s="16">
         <v>0</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <v>0</v>
       </c>
       <c r="I11" s="16" t="s">
@@ -1015,7 +1018,7 @@
       <c r="G12" s="16">
         <v>0</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="17">
         <v>0</v>
       </c>
       <c r="I12" s="16" t="s">
@@ -1050,7 +1053,7 @@
       <c r="G13" s="16">
         <v>0</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="17">
         <v>0</v>
       </c>
       <c r="I13" s="16" t="s">

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961F90AC-D9CC-46B4-A82C-FB6A8A2BEC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4D5F2B-447E-462E-8A32-009FD8FC3E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2856" yWindow="780" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="648" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
   <si>
     <t>(name)</t>
   </si>
@@ -222,6 +222,83 @@
   </si>
   <si>
     <t>Icon/Icon_SR</t>
+  </si>
+  <si>
+    <t>AC</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_AC_11</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유하고 있는 무기의 탄약을 체워줍니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_AC</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PrefabPath</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2DObject/AC_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/AD_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/GN_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/HK_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/MD_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/MG_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/PT_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/R0_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/RT2_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/SG_Drop</t>
+  </si>
+  <si>
+    <t>2DObject/SR_Drop</t>
+  </si>
+  <si>
+    <t>UseType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gun</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boom</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heel</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RepleAC</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -325,7 +402,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -374,11 +451,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -422,6 +508,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -686,6 +775,12 @@
       <c r="I2" s="15" t="s">
         <v>1</v>
       </c>
+      <c r="J2" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -715,6 +810,12 @@
       <c r="I3" s="18" t="s">
         <v>40</v>
       </c>
+      <c r="J3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -744,8 +845,12 @@
       <c r="I4" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="J4" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -779,8 +884,12 @@
       <c r="I5" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="J5" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -814,8 +923,12 @@
       <c r="I6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="J6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -849,8 +962,12 @@
       <c r="I7" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="J7" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -884,8 +1001,12 @@
       <c r="I8" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -919,8 +1040,12 @@
       <c r="I9" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="J9" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -954,8 +1079,12 @@
       <c r="I10" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -989,8 +1118,12 @@
       <c r="I11" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="J11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>73</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -1024,8 +1157,12 @@
       <c r="I12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="J12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>73</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -1059,25 +1196,51 @@
       <c r="I13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="J13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>73</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="A14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="16">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16">
+        <v>0</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>74</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4D5F2B-447E-462E-8A32-009FD8FC3E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E983C07-070C-4611-B983-1C860196E3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="648" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-684" yWindow="588" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="88">
   <si>
     <t>(name)</t>
   </si>
@@ -299,6 +299,47 @@
   <si>
     <t>RepleAC</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Anim_AttackPath</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Anim_ReloadPath</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>anim/Prey_MG</t>
+  </si>
+  <si>
+    <t>anim/Prey_MG_Reload</t>
+  </si>
+  <si>
+    <t>anim/Prey_R0</t>
+  </si>
+  <si>
+    <t>anim/Prey_R0_Reload</t>
+  </si>
+  <si>
+    <t>anim/Prey_RT</t>
+  </si>
+  <si>
+    <t>anim/Prey_RT2</t>
+  </si>
+  <si>
+    <t>anim/Prey_RT2_Reload</t>
+  </si>
+  <si>
+    <t>anim/Prey_RT_Reload</t>
+  </si>
+  <si>
+    <t>anim/Prey_SG_Reload</t>
+  </si>
+  <si>
+    <t>anim/Prey_SR</t>
+  </si>
+  <si>
+    <t>anim/Prey_SR_Reload</t>
   </si>
 </sst>
 </file>
@@ -781,6 +822,12 @@
       <c r="K2" s="19" t="s">
         <v>58</v>
       </c>
+      <c r="L2" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -816,6 +863,12 @@
       <c r="K3" s="18" t="s">
         <v>70</v>
       </c>
+      <c r="L3" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -851,8 +904,12 @@
       <c r="K4" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="L4" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>84</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
     </row>
@@ -890,8 +947,12 @@
       <c r="K5" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="L5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>83</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
     </row>
@@ -929,8 +990,12 @@
       <c r="K6" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="L6" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>80</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
     </row>
@@ -968,8 +1033,10 @@
       <c r="K7" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16" t="s">
+        <v>85</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
     </row>
@@ -1007,8 +1074,12 @@
       <c r="K8" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="L8" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
@@ -1046,8 +1117,12 @@
       <c r="K9" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>87</v>
+      </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
     </row>
@@ -1085,8 +1160,8 @@
       <c r="K10" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
     </row>
@@ -1124,8 +1199,8 @@
       <c r="K11" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
     </row>
@@ -1163,8 +1238,8 @@
       <c r="K12" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
     </row>
@@ -1202,8 +1277,8 @@
       <c r="K13" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
     </row>
@@ -1241,8 +1316,8 @@
       <c r="K14" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
     </row>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E983C07-070C-4611-B983-1C860196E3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682650E9-D3C4-4616-89CC-280B86D55B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-684" yWindow="588" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2436" yWindow="948" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="94">
   <si>
     <t>(name)</t>
   </si>
@@ -340,6 +340,29 @@
   </si>
   <si>
     <t>anim/Prey_SR_Reload</t>
+  </si>
+  <si>
+    <t>anim/Prey_SG</t>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalGun</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sniper</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>shotgun</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explosion</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -505,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -554,6 +577,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -828,6 +852,9 @@
       <c r="M2" s="19" t="s">
         <v>58</v>
       </c>
+      <c r="N2" s="19" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -869,6 +896,9 @@
       <c r="M3" s="18" t="s">
         <v>76</v>
       </c>
+      <c r="N3" s="20" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -910,7 +940,9 @@
       <c r="M4" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="N4" s="3"/>
+      <c r="N4" s="20" t="s">
+        <v>90</v>
+      </c>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
@@ -953,7 +985,9 @@
       <c r="M5" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="N5" s="3"/>
+      <c r="N5" s="20" t="s">
+        <v>90</v>
+      </c>
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
@@ -996,7 +1030,9 @@
       <c r="M6" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="N6" s="3"/>
+      <c r="N6" s="20" t="s">
+        <v>90</v>
+      </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
@@ -1033,11 +1069,15 @@
       <c r="K7" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="16"/>
+      <c r="L7" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="M7" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="N7" s="3"/>
+      <c r="N7" s="20" t="s">
+        <v>92</v>
+      </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
@@ -1080,7 +1120,9 @@
       <c r="M8" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="N8" s="3"/>
+      <c r="N8" s="20" t="s">
+        <v>90</v>
+      </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
@@ -1123,7 +1165,9 @@
       <c r="M9" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="N9" s="3"/>
+      <c r="N9" s="20" t="s">
+        <v>91</v>
+      </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
@@ -1162,7 +1206,9 @@
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
-      <c r="N10" s="3"/>
+      <c r="N10" s="20" t="s">
+        <v>93</v>
+      </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
@@ -1201,7 +1247,7 @@
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
-      <c r="N11" s="3"/>
+      <c r="N11" s="20"/>
       <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
@@ -1240,7 +1286,7 @@
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
-      <c r="N12" s="3"/>
+      <c r="N12" s="20"/>
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
@@ -1279,7 +1325,7 @@
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
-      <c r="N13" s="3"/>
+      <c r="N13" s="20"/>
       <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
@@ -1318,7 +1364,7 @@
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
-      <c r="N14" s="3"/>
+      <c r="N14" s="20"/>
       <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682650E9-D3C4-4616-89CC-280B86D55B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC28170-656C-4B99-827E-09F09D2BE4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2436" yWindow="948" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="95">
   <si>
     <t>(name)</t>
   </si>
@@ -357,11 +357,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>shotgun</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Explosion</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shotgun</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -829,10 +833,10 @@
         <v>34</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>34</v>
@@ -1076,7 +1080,7 @@
         <v>85</v>
       </c>
       <c r="N7" s="20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O7" s="3"/>
     </row>
@@ -1207,7 +1211,7 @@
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="N10" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O10" s="3"/>
     </row>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC28170-656C-4B99-827E-09F09D2BE4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A65BE38-3E7D-4FED-A2ED-17929D5BD052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2436" yWindow="948" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -918,7 +918,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="16">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F4" s="16">
         <v>40</v>
@@ -963,7 +963,7 @@
         <v>50</v>
       </c>
       <c r="E5" s="16">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F5" s="16">
         <v>50</v>
@@ -1053,7 +1053,7 @@
         <v>100</v>
       </c>
       <c r="E7" s="16">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F7" s="16">
         <v>30</v>
@@ -1098,7 +1098,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F8" s="16">
         <v>50</v>
@@ -1143,7 +1143,7 @@
         <v>100</v>
       </c>
       <c r="E9" s="16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F9" s="16">
         <v>80</v>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A65BE38-3E7D-4FED-A2ED-17929D5BD052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A9D63A-0520-42BB-ADC1-ECEAF3EABCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2436" yWindow="948" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3024" yWindow="2724" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -195,10 +195,6 @@
     <t>Icon/Icon_HK</t>
   </si>
   <si>
-    <t>Weapon_MK_9</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Weapon_AD_10</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -366,6 +362,10 @@
   </si>
   <si>
     <t>float</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_MD_9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -833,10 +833,10 @@
         <v>34</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>34</v>
@@ -845,19 +845,19 @@
         <v>1</v>
       </c>
       <c r="J2" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L2" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M2" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N2" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
@@ -889,19 +889,19 @@
         <v>40</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L3" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="M3" s="18" t="s">
-        <v>76</v>
-      </c>
       <c r="N3" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -930,22 +930,22 @@
         <v>-1</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N4" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O4" s="3"/>
     </row>
@@ -975,22 +975,22 @@
         <v>-1</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L5" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="M5" s="16" t="s">
-        <v>83</v>
-      </c>
       <c r="N5" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O5" s="3"/>
     </row>
@@ -1008,7 +1008,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="16">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F6" s="16">
         <v>65</v>
@@ -1020,22 +1020,22 @@
         <v>150</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L6" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="M6" s="16" t="s">
-        <v>80</v>
-      </c>
       <c r="N6" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -1053,10 +1053,10 @@
         <v>100</v>
       </c>
       <c r="E7" s="16">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F7" s="16">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G7" s="16">
         <v>12</v>
@@ -1065,22 +1065,22 @@
         <v>72</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N7" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O7" s="3"/>
     </row>
@@ -1098,7 +1098,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="16">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F8" s="16">
         <v>50</v>
@@ -1110,22 +1110,22 @@
         <v>200</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L8" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>78</v>
-      </c>
       <c r="N8" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O8" s="3"/>
     </row>
@@ -1155,22 +1155,22 @@
         <v>50</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L9" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="M9" s="16" t="s">
-        <v>87</v>
-      </c>
       <c r="N9" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O9" s="3"/>
     </row>
@@ -1203,15 +1203,15 @@
         <v>42</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="N10" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O10" s="3"/>
     </row>
@@ -1244,10 +1244,10 @@
         <v>43</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
@@ -1295,7 +1295,7 @@
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>31</v>
@@ -1322,10 +1322,10 @@
         <v>41</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
@@ -1334,13 +1334,13 @@
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
       <c r="A14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D14" s="16">
         <v>0</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A9D63A-0520-42BB-ADC1-ECEAF3EABCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F609E3-D488-42E7-9792-ADCB8013F427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3024" yWindow="2724" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2976" yWindow="3012" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -1098,7 +1098,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="16">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F8" s="16">
         <v>50</v>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F609E3-D488-42E7-9792-ADCB8013F427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD415D5-FB82-4ACF-8122-825AEE21A232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2976" yWindow="3012" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="1536" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -921,7 +921,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="16">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G4" s="16">
         <v>8</v>
@@ -966,7 +966,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="16">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G5" s="16">
         <v>8</v>
@@ -1011,7 +1011,7 @@
         <v>40</v>
       </c>
       <c r="F6" s="16">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G6" s="16">
         <v>30</v>
@@ -1050,13 +1050,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="16">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E7" s="16">
         <v>20</v>
       </c>
       <c r="F7" s="16">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G7" s="16">
         <v>12</v>
@@ -1146,7 +1146,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="16">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G9" s="16">
         <v>10</v>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD415D5-FB82-4ACF-8122-825AEE21A232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCE9571-0C77-4F38-98BD-C1466B1B2CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="1536" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="1056" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -1008,7 +1008,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="16">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F6" s="16">
         <v>55</v>
@@ -1098,7 +1098,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="16">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F8" s="16">
         <v>50</v>

--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCE9571-0C77-4F38-98BD-C1466B1B2CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DA2E7F-E72C-401E-AA77-402E934A85D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="1056" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -921,7 +921,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="16">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G4" s="16">
         <v>8</v>
@@ -966,7 +966,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="16">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G5" s="16">
         <v>8</v>
@@ -1011,7 +1011,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G6" s="16">
         <v>30</v>
@@ -1056,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="16">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G7" s="16">
         <v>12</v>
@@ -1146,7 +1146,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="16">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G9" s="16">
         <v>10</v>
